--- a/artfynd/Örans naturreservat artfynd.xlsx
+++ b/artfynd/Örans naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY112"/>
+  <dimension ref="A1:AZ112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669918</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84284767</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/645857</t>
         </is>
       </c>
     </row>
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84284918</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84286223</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90744</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/329884</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1662924</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1662925</t>
         </is>
       </c>
     </row>
@@ -1773,6 +1823,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129015881</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1888,6 +1943,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129015879</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1662926</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2111,6 +2176,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132393605</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521395</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2313,6 +2388,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521390</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14416226</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2545,6 +2630,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14409283</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2659,6 +2749,11 @@
       <c r="AY19" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90745</t>
         </is>
       </c>
     </row>
@@ -2762,6 +2857,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89781894</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2878,6 +2978,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1662927</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2993,6 +3098,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79738494</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3105,6 +3215,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123944568</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3216,6 +3331,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3416580</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3327,6 +3447,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4887450</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3434,6 +3559,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103740583</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3540,6 +3670,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1922150</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3646,6 +3781,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2015013</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3747,6 +3887,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521396</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3848,6 +3993,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521400</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3949,6 +4099,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521403</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4079,6 +4234,11 @@
           <t>Södertörnsekologernas groddjursprojekt 2008</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26884</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4204,6 +4364,11 @@
           <t>Södertörnsekologernas groddjursprojekt 2008</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6810</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4329,6 +4494,11 @@
           <t>Södertörnsekologernas groddjursprojekt 2008</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26882</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4435,6 +4605,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/38106</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4555,6 +4730,11 @@
           <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62707467</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4697,6 +4877,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86884446</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4815,6 +5000,11 @@
       <c r="AY38" t="inlineStr">
         <is>
           <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111800151</t>
         </is>
       </c>
     </row>
@@ -4918,6 +5108,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81204323</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5019,6 +5214,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521383</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5120,6 +5320,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521394</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5221,6 +5426,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521398</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5333,6 +5543,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132236790</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5432,6 +5647,11 @@
       <c r="AY44" t="inlineStr">
         <is>
           <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521397</t>
         </is>
       </c>
     </row>
@@ -5534,6 +5754,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60005717</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5635,6 +5860,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521382</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5755,6 +5985,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85847244</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5866,6 +6101,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95823219</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5979,6 +6219,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60746458</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6094,6 +6339,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85847173</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6195,6 +6445,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521409</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6322,6 +6577,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54750873</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6439,6 +6699,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60746380</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6548,6 +6813,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54666417</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6657,6 +6927,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60656211</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6758,6 +7033,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521399</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6859,6 +7139,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521385</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6971,6 +7256,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124097424</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7083,6 +7373,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124097902</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7184,6 +7479,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521381</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7285,6 +7585,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521379</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7386,6 +7691,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521380</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7506,6 +7816,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127905662</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7607,6 +7922,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521410</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7708,6 +8028,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521406</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7809,6 +8134,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521368</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7910,6 +8240,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521405</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8011,6 +8346,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521378</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8110,6 +8450,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129754514</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8211,6 +8556,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521412</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8312,6 +8662,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521377</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8413,6 +8768,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521376</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8514,6 +8874,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521375</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8615,6 +8980,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521374</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8716,6 +9086,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521373</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8834,6 +9209,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54750815</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8947,6 +9327,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54750796</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9048,6 +9433,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521371</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9149,6 +9539,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521372</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9250,6 +9645,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521369</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9365,6 +9765,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123865715</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9476,6 +9881,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101495558</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9591,6 +10001,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76887532</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9702,6 +10117,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85370266</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9813,6 +10233,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110786011</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9929,6 +10354,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126472963</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10040,6 +10470,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101174483</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10154,6 +10589,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71123739</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10265,6 +10705,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101174479</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10376,6 +10821,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85896906</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10498,6 +10948,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71369660</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10609,6 +11064,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134280726</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10723,6 +11183,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71369726</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10841,6 +11306,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71369714</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10952,6 +11422,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101495728</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11063,6 +11538,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133630289</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11177,6 +11657,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70963662</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11308,6 +11793,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71123729</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11419,6 +11909,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131645049</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11533,6 +12028,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70835524</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11644,6 +12144,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126473228</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11755,6 +12260,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132180810</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11866,6 +12376,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129408193</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11977,6 +12492,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101495508</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12092,6 +12612,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74296781</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12203,6 +12728,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116149552</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12321,6 +12851,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70835625</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12436,6 +12971,11 @@
           <t>Nordens Ark - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120125746</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12547,6 +13087,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56604</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12672,6 +13217,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114998</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12774,6 +13324,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1419817</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12882,8 +13437,126 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108787205</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>